--- a/用卷/2017.xlsx
+++ b/用卷/2017.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Desktop\高考用卷\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27B466A7-E67F-4172-9562-F6F9B94459D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04476228-33C5-4291-B809-A65175EEF6A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1169,7 +1169,7 @@
         <v>42</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="D33" s="4"/>
     </row>
